--- a/documentation/Agile Stories.xlsx
+++ b/documentation/Agile Stories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14dea98c0cd94b0f/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a94f2f373779cfa/Documents/23 - 24/EECS 581/P3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7036133-E0C1-45BB-9354-3FE6D1B3EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{CB749020-4EEF-450B-B970-563F0EBD7ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{430BA18A-BCB7-47B4-96F9-E0145757923A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D8055946-DC2C-4141-B775-8B706DB1B0A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3550263F-978F-47BA-AB04-E85B83F0935A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,116 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+  <si>
+    <t>Story #</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>Story Source</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>EECS 330 SP25</t>
+  </si>
+  <si>
+    <t>EECS 348 FA24</t>
+  </si>
+  <si>
+    <t>EECS 268 SP24</t>
+  </si>
+  <si>
+    <t>Weekly basic python programs to increase understanding of programming. Involves implementation of basic data structures through object oriented programming and interaction between multiple python files.</t>
+  </si>
+  <si>
+    <t>Implement a graph data structure in C++ using properties inherited from vectors, linked lists, queues, stacks and hash tables. Implementation involves proper memory management across data structures.</t>
+  </si>
+  <si>
+    <t>Implementation of a basic calculator in C++ that can parse inputs, detect improper input, and do simple arithmatic operations on integer and decimal numbers.</t>
+  </si>
+  <si>
+    <t>EECS 388 SP25</t>
+  </si>
+  <si>
+    <t>EECS 678 FA25</t>
+  </si>
+  <si>
+    <t>EECS 510 FA25</t>
+  </si>
+  <si>
+    <t>EECS 565 SP25</t>
+  </si>
+  <si>
+    <t>EECS 563 SP25</t>
+  </si>
+  <si>
+    <t>EECS 447 SP26</t>
+  </si>
+  <si>
+    <t>EECS 677 FA26</t>
+  </si>
+  <si>
+    <t>EECS 581 FA26</t>
+  </si>
+  <si>
+    <t>C++ implementation of a control unit for a toy car. Separate code analyzes video input, implementation involves making decisions on turning and starting/stopping the car.</t>
+  </si>
+  <si>
+    <t>Used C++ to design and create a UNIX like shell that parses commands and executes tasks based on input. Recognizes basic shell commands and starting/stopping of processes as well as piping.</t>
+  </si>
+  <si>
+    <t>Designing a formal langauge defined by a formal grammar and a finite state machine. Implemented the formal language with a data structure that accepts strings considered part of the language.</t>
+  </si>
+  <si>
+    <t>Implemented a program to perform a statistical attack on a polyalphabetic cipher to determine an encryption key of both known or unknown size.</t>
+  </si>
+  <si>
+    <t>Used programming sockets to establish TCP and UDP connections between a client and a host. Each connection was able to send and receive information without working out of turn.</t>
+  </si>
+  <si>
+    <t>Created a webpage that displays and modifies information for a connected database using API calls. Used SQL to design and create database and JavaScript to create the webpage.</t>
+  </si>
+  <si>
+    <t>Implemented code to do static analysis of programs in LLVM intermediate representation. The project broke down code into basic executable blocks and analyzed each to determine if a secret value was leaked.</t>
+  </si>
+  <si>
+    <t>Developed a version of the minesweeper game using Pygame. The project is intended function as similarly to the original minesweeper as possible including tile digging &amp; flagging, difficulty selection, and time keeping.</t>
+  </si>
+  <si>
+    <t>Created a project capable of scheduling CPU time for input processes according to different scheduling algorithms including versions of preemptive scheduling.</t>
+  </si>
+  <si>
+    <t>EECS 140 SP24</t>
+  </si>
+  <si>
+    <t>VHDL project for implementing look up table logic on FPGA boards for various types of latches and flip flops.</t>
+  </si>
+  <si>
+    <t>EECS 649 FA26</t>
+  </si>
+  <si>
+    <t>Created an AI solver for the DaMert 3D squares puzzle using depth first search with heuristic based decision making.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -69,8 +175,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,10 +512,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA45AEE1-B4D2-484A-8E47-84E09CA8AEC8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A9BF52-567A-4D63-A7BE-F9B1A6C83D9E}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="194.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documentation/Agile Stories.xlsx
+++ b/documentation/Agile Stories.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t xml:space="preserve">Story #</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t xml:space="preserve">Designing a formal langauge defined by a formal grammar and a finite state machine. Implemented the formal language with a data structure that accepts strings considered part of the language.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity Scene Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creation of a C# class in Unity to load and unload scenes. Scenes are collections of GameObjects and scripts attached to them.</t>
   </si>
   <si>
     <t xml:space="preserve">Used C++ to design and create a UNIX like shell that parses commands and executes tasks based on input. Recognizes basic shell commands and starting/stopping of processes as well as piping.</t>
@@ -424,7 +430,7 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="194.14"/>
   </cols>
   <sheetData>
@@ -603,6 +609,12 @@
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -615,7 +627,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -626,10 +638,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -640,10 +652,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -654,10 +666,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -668,10 +680,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -682,10 +694,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/Agile Stories.xlsx
+++ b/documentation/Agile Stories.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Implemented code to do static analysis of programs in LLVM intermediate representation. The project broke down code into basic executable blocks and analyzed each to determine if a secret value was leaked.</t>
   </si>
   <si>
-    <t xml:space="preserve">Input Manager</t>
+    <t xml:space="preserve">Personal Unity Project – Input Manager</t>
   </si>
   <si>
     <t xml:space="preserve">Create a system for managing user input (keyboard/mouse/controller) in the Unity game engine, using official libraries/packages. This includes detecting inputs, but not applying any logic after receiving an input.</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Created an AI solver for the DaMert 3D squares puzzle using depth first search with heuristic based decision making.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity Save System</t>
+    <t xml:space="preserve">Personal Unity Project – Unity Save System</t>
   </si>
   <si>
     <t xml:space="preserve">Implementation of saving and retrieving objects to and from files in the Unity game engine. This includes defining the object’s fields, collecting data into the fields, and saving it (and going in reverse, too).</t>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Designing a formal langauge defined by a formal grammar and a finite state machine. Implemented the formal language with a data structure that accepts strings considered part of the language.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity Scene Manager</t>
+    <t xml:space="preserve">Personal Unity Project – Unity Scene Manager</t>
   </si>
   <si>
     <t xml:space="preserve">Creation of a C# class in Unity to load and unload scenes. Scenes are collections of GameObjects and scripts attached to them.</t>
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Used C++ to design and create a UNIX like shell that parses commands and executes tasks based on input. Recognizes basic shell commands and starting/stopping of processes as well as piping.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tile-Based Pathfinding Algorithm</t>
+    <t xml:space="preserve">Personal Unity Project – Tile-Based Pathfinding Algorithm</t>
   </si>
   <si>
     <t xml:space="preserve">Implement movement across tiles using the A* path finding algorithm, accounting for the possibility that different tiles might have different “movement costs.”</t>
@@ -429,8 +429,8 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="194.14"/>
   </cols>
   <sheetData>
